--- a/TestData/TMTT0005430_TimeRecorderFunctionalities.xlsx
+++ b/TestData/TMTT0005430_TimeRecorderFunctionalities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461E73D3-7C04-4644-9F2D-126755DA7DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A0E4FA-2914-41DF-A119-F5533C85897B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -18,10 +18,21 @@
     <sheet name="Project_Title" sheetId="11" r:id="rId3"/>
     <sheet name="Update_Timer" sheetId="13" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -796,14 +807,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -816,14 +827,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -837,13 +848,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -851,7 +862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -868,9 +879,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -884,7 +895,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -898,7 +909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D8" s="3"/>
     </row>
   </sheetData>
